--- a/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -2554,7 +2554,7 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>-12100</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>405800</v>
+        <v>393700</v>
       </c>
       <c r="E76" s="3">
         <v>429500</v>

--- a/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>BLFY</t>
   </si>
@@ -656,80 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43220</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>42855</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42490</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E8" s="3">
         <v>62400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>61600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>64800</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,9 +745,12 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -775,9 +781,12 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,9 +905,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -922,9 +941,12 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -955,9 +977,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,26 +993,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E17" s="3">
         <v>9600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,27 +1026,30 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E18" s="3">
         <v>52800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>41700</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,9 +1062,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,26 +1081,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-50100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-72200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-75900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,27 +1114,30 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E21" s="3">
         <v>5400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-37400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9200</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,9 +1150,12 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1147,75 +1186,84 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,27 +1510,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E32" s="3">
         <v>50100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>72200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>75900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,42 +1546,48 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43220</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>42855</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42490</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,74 +1730,81 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E41" s="3">
         <v>41200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>193400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>316400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>124000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E42" s="3">
         <v>16100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1743,9 +1835,12 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1776,9 +1871,12 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1809,9 +1907,12 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1842,9 +1943,12 @@
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1875,42 +1979,48 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E48" s="3">
         <v>55700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1920,11 +2030,11 @@
       <c r="E49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G49" s="3">
-        <v>15500</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>15500</v>
@@ -1935,15 +2045,18 @@
       <c r="J49" s="3">
         <v>15500</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>15500</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,24 +2123,27 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>5300</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
@@ -2034,15 +2153,18 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2045000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2043300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1914200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1942500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1854100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1696000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1684100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1547800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,8 +2266,9 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2169,9 +2299,12 @@
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2202,26 +2335,29 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E59" s="3">
         <v>27300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25500</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2235,9 +2371,12 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2268,27 +2407,30 @@
       <c r="L60" s="3">
         <v>0</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E61" s="3">
         <v>9300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2301,9 +2443,12 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2313,15 +2458,15 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1689300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1649600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1484700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1736900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1616500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1470600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1463400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1333000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,27 +2783,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E72" s="3">
         <v>171800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>169500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>205800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>237300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,9 +2819,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>355600</v>
+      </c>
+      <c r="E76" s="3">
         <v>393700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>429500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>205600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>237600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>225400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>220600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>214700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43220</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>42855</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42490</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,25 +3095,26 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E83" s="3">
         <v>2700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1900</v>
       </c>
       <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>1900</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2930,9 +3128,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,27 +3308,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5400</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,9 +3344,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,26 +3363,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,9 +3396,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,27 +3468,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-306200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>101400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3504,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,27 +3664,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E100" s="3">
         <v>151200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>92300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>141900</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,9 +3700,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3482,33 +3730,36 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-152300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-123000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>192400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>89600</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,7 +3772,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>BLFY</t>
   </si>
@@ -663,7 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -697,11 +698,11 @@
       <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
-        <v>43220</v>
-      </c>
-      <c r="J7" s="2">
-        <v>42855</v>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2">
         <v>42490</v>
@@ -719,19 +720,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>79100</v>
+        <v>44200</v>
       </c>
       <c r="E8" s="3">
-        <v>62400</v>
+        <v>55500</v>
       </c>
       <c r="F8" s="3">
-        <v>56100</v>
+        <v>47900</v>
       </c>
       <c r="G8" s="3">
-        <v>61600</v>
+        <v>25000</v>
       </c>
       <c r="H8" s="3">
-        <v>64800</v>
+        <v>44300</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -790,20 +791,20 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>55500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>47900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>44300</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -914,26 +915,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>16300</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -951,19 +952,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1000,19 +1001,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>51800</v>
+      </c>
+      <c r="G17" s="3">
+        <v>47700</v>
+      </c>
+      <c r="H17" s="3">
         <v>36700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>9600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>10600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>25100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>23200</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1036,19 +1037,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>42400</v>
+        <v>-6600</v>
       </c>
       <c r="E18" s="3">
-        <v>52800</v>
+        <v>3100</v>
       </c>
       <c r="F18" s="3">
-        <v>45500</v>
+        <v>-3900</v>
       </c>
       <c r="G18" s="3">
-        <v>36500</v>
+        <v>-22700</v>
       </c>
       <c r="H18" s="3">
-        <v>41700</v>
+        <v>7500</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1088,19 +1089,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-49800</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>-50100</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>-72200</v>
+        <v>500</v>
       </c>
       <c r="G20" s="3">
-        <v>-75900</v>
+        <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>-34300</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1130,19 +1131,19 @@
         <v>5400</v>
       </c>
       <c r="F21" s="3">
-        <v>-24400</v>
+        <v>-2000</v>
       </c>
       <c r="G21" s="3">
-        <v>-37400</v>
+        <v>-21100</v>
       </c>
       <c r="H21" s="3">
         <v>9200</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1159,26 +1160,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1210,11 +1211,11 @@
       <c r="H23" s="3">
         <v>7300</v>
       </c>
-      <c r="I23" s="3">
-        <v>12400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>10400</v>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>9300</v>
@@ -1231,8 +1232,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
@@ -1246,11 +1247,11 @@
       <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
-        <v>6100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3600</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>3200</v>
@@ -1318,11 +1319,11 @@
       <c r="H26" s="3">
         <v>5500</v>
       </c>
-      <c r="I26" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>6900</v>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>6200</v>
@@ -1354,11 +1355,11 @@
       <c r="H27" s="3">
         <v>5500</v>
       </c>
-      <c r="I27" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>6900</v>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>6200</v>
@@ -1520,19 +1521,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>49800</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>50100</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>72200</v>
+        <v>-500</v>
       </c>
       <c r="G32" s="3">
-        <v>75900</v>
+        <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>34300</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1570,11 +1571,11 @@
       <c r="H33" s="3">
         <v>5500</v>
       </c>
-      <c r="I33" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>6900</v>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>6200</v>
@@ -1642,11 +1643,11 @@
       <c r="H35" s="3">
         <v>5500</v>
       </c>
-      <c r="I35" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>6900</v>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>6200</v>
@@ -1683,11 +1684,11 @@
       <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
-        <v>43220</v>
-      </c>
-      <c r="J38" s="2">
-        <v>42855</v>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2">
         <v>42490</v>
@@ -1751,11 +1752,11 @@
       <c r="H41" s="3">
         <v>124000</v>
       </c>
-      <c r="I41" s="3">
-        <v>30900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>29400</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>25600</v>
@@ -1773,25 +1774,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20300</v>
+        <v>9000</v>
       </c>
       <c r="E42" s="3">
-        <v>16100</v>
+        <v>11100</v>
       </c>
       <c r="F42" s="3">
-        <v>10200</v>
+        <v>1300</v>
       </c>
       <c r="G42" s="3">
-        <v>16900</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>8500</v>
@@ -1808,26 +1809,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1845,25 +1846,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1881,25 +1882,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>5400</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -1917,25 +1918,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>63300</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>60100</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>200100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>328200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
+        <v>131400</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1953,25 +1954,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>337400</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>364000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>358400</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>251600</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>218100</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2003,11 +2004,11 @@
       <c r="H48" s="3">
         <v>32300</v>
       </c>
-      <c r="I48" s="3">
-        <v>33000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>33500</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>34900</v>
@@ -2024,14 +2025,14 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -2039,11 +2040,11 @@
       <c r="H49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
-        <v>15500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15500</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>15500</v>
@@ -2132,26 +2133,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>31800</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="G52" s="3">
-        <v>5300</v>
+        <v>41200</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>43900</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2219,11 +2220,11 @@
       <c r="H54" s="3">
         <v>1854100</v>
       </c>
-      <c r="I54" s="3">
-        <v>1696000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1684100</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>1547800</v>
@@ -2273,25 +2274,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1244900</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1288900</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1247000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1356200</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>1295000</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2309,25 +2310,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>331900</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2344,20 +2345,20 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>26800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>27300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>26700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>25500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2381,25 +2382,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1576800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1288900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1248600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1361700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+        <v>1295000</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2417,19 +2418,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8900</v>
+        <v>93900</v>
       </c>
       <c r="E61" s="3">
-        <v>9300</v>
+        <v>337800</v>
       </c>
       <c r="F61" s="3">
-        <v>9600</v>
+        <v>212200</v>
       </c>
       <c r="G61" s="3">
-        <v>10800</v>
+        <v>354900</v>
       </c>
       <c r="H61" s="3">
-        <v>12200</v>
+        <v>296900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2452,20 +2453,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>22300</v>
       </c>
       <c r="G62" s="3">
-        <v>1800</v>
+        <v>18400</v>
       </c>
       <c r="H62" s="3">
-        <v>1900</v>
+        <v>22600</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2611,11 +2612,11 @@
       <c r="H66" s="3">
         <v>1616500</v>
       </c>
-      <c r="I66" s="3">
-        <v>1470600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1463400</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>1333000</v>
@@ -2951,11 +2952,11 @@
       <c r="H76" s="3">
         <v>237600</v>
       </c>
-      <c r="I76" s="3">
-        <v>225400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>220600</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>214700</v>
@@ -3028,11 +3029,11 @@
       <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
-        <v>43220</v>
-      </c>
-      <c r="J80" s="2">
-        <v>42855</v>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2">
         <v>42490</v>
@@ -3064,11 +3065,11 @@
       <c r="H81" s="3">
         <v>5500</v>
       </c>
-      <c r="I81" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>6900</v>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>6200</v>
@@ -3709,26 +3710,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3760,11 +3761,11 @@
       <c r="H102" s="3">
         <v>89600</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>BLFY</t>
   </si>
@@ -656,87 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
         <v>42490</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E8" s="3">
         <v>44200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>55500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>44300</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -749,9 +752,12 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,30 +791,33 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E10" s="3">
         <v>44200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>44300</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,9 +830,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +850,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -873,9 +886,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,9 +925,12 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -921,23 +940,23 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>22400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -945,29 +964,32 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E15" s="3">
         <v>2900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1900</v>
       </c>
       <c r="H15" s="3">
         <v>1900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -981,9 +1003,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -995,29 +1020,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E17" s="3">
         <v>50800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>52400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36700</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,30 +1056,33 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7500</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1066,9 +1095,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1083,29 +1115,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,35 +1151,38 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-21100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9200</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1154,9 +1190,12 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1181,8 +1220,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1190,81 +1229,90 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7300</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>9300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1298,81 +1346,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5500</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>6200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-36300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5500</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>6200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1406,9 +1463,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1442,9 +1502,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1478,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1514,30 +1580,33 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,45 +1619,51 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5500</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>6200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1622,86 +1697,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5500</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>6200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2">
         <v>42490</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1716,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1732,62 +1817,66 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E41" s="3">
         <v>46000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>193400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>316400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>124000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>25600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>9000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -1795,17 +1884,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>8500</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1830,8 +1922,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1839,35 +1931,38 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1875,35 +1970,38 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -1911,35 +2009,38 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E46" s="3">
         <v>63300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>328200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>131400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
+      <c r="K46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -1947,35 +2048,38 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>347900</v>
+      </c>
+      <c r="E47" s="3">
         <v>337400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>364000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>358400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>251600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>218100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -1983,45 +2087,51 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E48" s="3">
         <v>57600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>34900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2038,26 +2148,29 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>15500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2091,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2127,45 +2243,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E52" s="3">
         <v>40100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>43900</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2199,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2060700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2045000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2043300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1914200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1942500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1854100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>1547800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2252,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2268,34 +2397,35 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1343300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1244900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1288900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1247000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1356200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1295000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2303,35 +2433,38 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>331900</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2339,9 +2472,12 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2375,35 +2511,38 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1343300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1576800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1288900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1248600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1361700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1295000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -2411,30 +2550,33 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>364700</v>
+      </c>
+      <c r="E61" s="3">
         <v>93900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>337800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>212200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>354900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>296900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2447,30 +2589,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E62" s="3">
         <v>17600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>22300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2483,9 +2628,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2519,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2591,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1728500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1689300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1649600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1484700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1736900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1616500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>1333000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2644,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2679,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2715,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2751,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2787,30 +2957,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>164300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>171800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>169500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>205800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>237300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2823,9 +2996,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2859,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2895,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2931,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>332200</v>
+      </c>
+      <c r="E76" s="3">
         <v>355600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>393700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>429500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>205600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>237600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>214700</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3003,86 +3191,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2">
         <v>42490</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5500</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>6200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3097,28 +3294,29 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1900</v>
       </c>
       <c r="H83" s="3">
         <v>1900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>1900</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3132,9 +3330,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3168,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3204,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3240,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3276,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3312,30 +3525,33 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5400</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,9 +3564,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3365,29 +3584,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,9 +3620,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3472,30 +3698,33 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>10300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-306200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-105300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>101400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,9 +3737,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3525,8 +3757,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3560,9 +3793,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3596,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3632,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3668,30 +3910,33 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>6700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>151200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>92300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>141900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3704,9 +3949,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3731,44 +3979,47 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>4800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-152300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-123000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>192400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>89600</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -3776,7 +4027,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLFY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>BLFY</t>
   </si>
@@ -1863,7 +1863,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E42" s="3">
         <v>9000</v>
@@ -2019,7 +2019,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>50500</v>
+        <v>59300</v>
       </c>
       <c r="E46" s="3">
         <v>63300</v>
@@ -2253,7 +2253,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>38800</v>
+        <v>30000</v>
       </c>
       <c r="E52" s="3">
         <v>40100</v>
@@ -2443,10 +2443,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>293300</v>
       </c>
       <c r="E58" s="3">
-        <v>331900</v>
+        <v>1500</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2521,10 +2521,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1343300</v>
+        <v>1636600</v>
       </c>
       <c r="E60" s="3">
-        <v>1576800</v>
+        <v>1246400</v>
       </c>
       <c r="F60" s="3">
         <v>1288900</v>
@@ -2560,10 +2560,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>364700</v>
+        <v>71900</v>
       </c>
       <c r="E61" s="3">
-        <v>93900</v>
+        <v>424300</v>
       </c>
       <c r="F61" s="3">
         <v>337800</v>
@@ -2599,7 +2599,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20500</v>
+        <v>18900</v>
       </c>
       <c r="E62" s="3">
         <v>17600</v>
@@ -2966,8 +2966,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>152400</v>
       </c>
       <c r="E72" s="3">
         <v>164300</v>
@@ -3300,8 +3300,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>3100</v>
       </c>
       <c r="E83" s="3">
         <v>2900</v>
@@ -3534,8 +3534,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>5100</v>
       </c>
       <c r="E89" s="3">
         <v>-12100</v>
@@ -3590,8 +3590,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-5600</v>
@@ -3707,8 +3707,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-30000</v>
       </c>
       <c r="E94" s="3">
         <v>10300</v>
@@ -3919,8 +3919,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>21400</v>
       </c>
       <c r="E100" s="3">
         <v>6700</v>
@@ -3998,7 +3998,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="E102" s="3">
         <v>4800</v>
